--- a/Fase 2/Evidencias Proyecto/Evidencia de documentación/Documentos de Gestión/Carta_Gantt_Proyecto.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencia de documentación/Documentos de Gestión/Carta_Gantt_Proyecto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebax\Downloads\Capstone-main (2)\Capstone-main\Fase 2\Evidencias Proyecto\Evidencia de documentación\Documentos de Gestión\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebax\Downloads\Capstone-main (3)\Capstone-main\Fase 2\Evidencias Proyecto\Evidencia de documentación\Documentos de Gestión\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1468A8-B21A-4740-80B1-23C91038AABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7944AD05-32D0-4789-A8A5-F7B7D129A606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carta Gantt" sheetId="1" r:id="rId1"/>
@@ -1006,7 +1006,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1070,9 +1070,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1099,9 +1096,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1126,9 +1120,6 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1138,9 +1129,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1148,19 +1136,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1188,6 +1167,9 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1215,9 +1197,6 @@
     </xf>
     <xf numFmtId="9" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1457,76 +1436,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="70"/>
-      <c r="T1" s="70"/>
-      <c r="U1" s="70"/>
-      <c r="V1" s="70"/>
-      <c r="W1" s="70"/>
-      <c r="X1" s="70"/>
-      <c r="Y1" s="70"/>
-      <c r="Z1" s="70"/>
-      <c r="AA1" s="70"/>
-      <c r="AB1" s="70"/>
-      <c r="AC1" s="70"/>
-      <c r="AD1" s="70"/>
-      <c r="AE1" s="70"/>
-      <c r="AF1" s="70"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
+      <c r="Z1" s="64"/>
+      <c r="AA1" s="64"/>
+      <c r="AB1" s="64"/>
+      <c r="AC1" s="64"/>
+      <c r="AD1" s="64"/>
+      <c r="AE1" s="64"/>
+      <c r="AF1" s="64"/>
     </row>
     <row r="2" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="70"/>
-      <c r="T2" s="70"/>
-      <c r="U2" s="70"/>
-      <c r="V2" s="70"/>
-      <c r="W2" s="70"/>
-      <c r="X2" s="70"/>
-      <c r="Y2" s="70"/>
-      <c r="Z2" s="70"/>
-      <c r="AA2" s="70"/>
-      <c r="AB2" s="70"/>
-      <c r="AC2" s="70"/>
-      <c r="AD2" s="70"/>
-      <c r="AE2" s="70"/>
-      <c r="AF2" s="70"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="64"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="64"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="64"/>
+      <c r="W2" s="64"/>
+      <c r="X2" s="64"/>
+      <c r="Y2" s="64"/>
+      <c r="Z2" s="64"/>
+      <c r="AA2" s="64"/>
+      <c r="AB2" s="64"/>
+      <c r="AC2" s="64"/>
+      <c r="AD2" s="64"/>
+      <c r="AE2" s="64"/>
+      <c r="AF2" s="64"/>
       <c r="AH2" s="5" t="s">
         <v>19</v>
       </c>
@@ -1559,50 +1538,50 @@
       </c>
     </row>
     <row r="4" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="74" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="72" t="s">
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="72" t="s">
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="75" t="s">
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="W4" s="73"/>
-      <c r="X4" s="73"/>
-      <c r="Y4" s="73"/>
-      <c r="Z4" s="73"/>
-      <c r="AA4" s="73"/>
-      <c r="AB4" s="73"/>
-      <c r="AC4" s="73"/>
-      <c r="AD4" s="73"/>
-      <c r="AE4" s="76" t="s">
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="AF4" s="73"/>
+      <c r="AF4" s="67"/>
     </row>
     <row r="5" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
@@ -1709,7 +1688,7 @@
       <c r="A6" s="8">
         <v>1</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="9" t="s">
@@ -1720,7 +1699,7 @@
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="25" t="s">
         <v>128</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -1736,42 +1715,42 @@
         <f t="shared" ref="K6:K49" si="0">J6-I6+1</f>
         <v>1</v>
       </c>
-      <c r="L6" s="30">
+      <c r="L6" s="29">
         <f t="shared" ref="L6:L49" si="1">$B$3+(I6-1)*7</f>
         <v>46261</v>
       </c>
-      <c r="M6" s="30">
+      <c r="M6" s="29">
         <f t="shared" ref="M6:M49" si="2">$B$3+(J6)*7-1</f>
         <v>46267</v>
       </c>
       <c r="N6" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="34"/>
-      <c r="T6" s="34"/>
-      <c r="U6" s="34"/>
-      <c r="V6" s="34"/>
-      <c r="W6" s="34"/>
-      <c r="X6" s="34"/>
-      <c r="Y6" s="34"/>
-      <c r="Z6" s="34"/>
-      <c r="AA6" s="34"/>
-      <c r="AB6" s="34"/>
-      <c r="AC6" s="34"/>
-      <c r="AD6" s="34"/>
-      <c r="AE6" s="34"/>
-      <c r="AF6" s="34"/>
-      <c r="AG6" s="81"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="33"/>
+      <c r="S6" s="33"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="33"/>
+      <c r="V6" s="33"/>
+      <c r="W6" s="33"/>
+      <c r="X6" s="33"/>
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="33"/>
+      <c r="AA6" s="33"/>
+      <c r="AB6" s="33"/>
+      <c r="AC6" s="33"/>
+      <c r="AD6" s="33"/>
+      <c r="AE6" s="33"/>
+      <c r="AF6" s="33"/>
+      <c r="AG6" s="62"/>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>2</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="9" t="s">
@@ -1782,7 +1761,7 @@
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="25" t="s">
         <v>145</v>
       </c>
       <c r="H7" s="8" t="s">
@@ -1798,42 +1777,42 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="29">
         <f t="shared" si="1"/>
         <v>46247</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="29">
         <f t="shared" si="2"/>
         <v>46260</v>
       </c>
       <c r="N7" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="34"/>
-      <c r="U7" s="34"/>
-      <c r="V7" s="34"/>
-      <c r="W7" s="34"/>
-      <c r="X7" s="34"/>
-      <c r="Y7" s="34"/>
-      <c r="Z7" s="34"/>
-      <c r="AA7" s="34"/>
-      <c r="AB7" s="34"/>
-      <c r="AC7" s="34"/>
-      <c r="AD7" s="34"/>
-      <c r="AE7" s="34"/>
-      <c r="AF7" s="34"/>
-      <c r="AG7" s="81"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="33"/>
+      <c r="R7" s="33"/>
+      <c r="S7" s="33"/>
+      <c r="T7" s="33"/>
+      <c r="U7" s="33"/>
+      <c r="V7" s="33"/>
+      <c r="W7" s="33"/>
+      <c r="X7" s="33"/>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="33"/>
+      <c r="AA7" s="33"/>
+      <c r="AB7" s="33"/>
+      <c r="AC7" s="33"/>
+      <c r="AD7" s="33"/>
+      <c r="AE7" s="33"/>
+      <c r="AF7" s="33"/>
+      <c r="AG7" s="62"/>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>3</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="9" t="s">
@@ -1844,7 +1823,7 @@
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="25" t="s">
         <v>128</v>
       </c>
       <c r="H8" s="8" t="s">
@@ -1860,42 +1839,42 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="29">
         <f t="shared" si="1"/>
         <v>46247</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="29">
         <f t="shared" si="2"/>
         <v>46260</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="34"/>
-      <c r="X8" s="34"/>
-      <c r="Y8" s="34"/>
-      <c r="Z8" s="34"/>
-      <c r="AA8" s="34"/>
-      <c r="AB8" s="34"/>
-      <c r="AC8" s="34"/>
-      <c r="AD8" s="34"/>
-      <c r="AE8" s="34"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="81"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="33"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="33"/>
+      <c r="AC8" s="33"/>
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="33"/>
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="62"/>
     </row>
     <row r="9" spans="1:35" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>4</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
@@ -1906,7 +1885,7 @@
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="25" t="s">
         <v>157</v>
       </c>
       <c r="H9" s="8" t="s">
@@ -1922,42 +1901,42 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="29">
         <f t="shared" si="1"/>
         <v>46254</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="29">
         <f t="shared" si="2"/>
         <v>46267</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="O9" s="34"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="34"/>
-      <c r="W9" s="34"/>
-      <c r="X9" s="34"/>
-      <c r="Y9" s="34"/>
-      <c r="Z9" s="34"/>
-      <c r="AA9" s="34"/>
-      <c r="AB9" s="34"/>
-      <c r="AC9" s="34"/>
-      <c r="AD9" s="34"/>
-      <c r="AE9" s="34"/>
-      <c r="AF9" s="34"/>
-      <c r="AG9" s="81"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="33"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="33"/>
+      <c r="V9" s="33"/>
+      <c r="W9" s="33"/>
+      <c r="X9" s="33"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="33"/>
+      <c r="AA9" s="33"/>
+      <c r="AB9" s="33"/>
+      <c r="AC9" s="33"/>
+      <c r="AD9" s="33"/>
+      <c r="AE9" s="33"/>
+      <c r="AF9" s="33"/>
+      <c r="AG9" s="62"/>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>5</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="9" t="s">
@@ -1968,7 +1947,7 @@
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="25" t="s">
         <v>159</v>
       </c>
       <c r="H10" s="8" t="s">
@@ -1984,42 +1963,42 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="29">
         <f t="shared" si="1"/>
         <v>46254</v>
       </c>
-      <c r="M10" s="30">
+      <c r="M10" s="29">
         <f t="shared" si="2"/>
         <v>46267</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="O10" s="34"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
-      <c r="U10" s="34"/>
-      <c r="V10" s="34"/>
-      <c r="W10" s="34"/>
-      <c r="X10" s="34"/>
-      <c r="Y10" s="34"/>
-      <c r="Z10" s="34"/>
-      <c r="AA10" s="34"/>
-      <c r="AB10" s="34"/>
-      <c r="AC10" s="34"/>
-      <c r="AD10" s="34"/>
-      <c r="AE10" s="34"/>
-      <c r="AF10" s="34"/>
-      <c r="AG10" s="81"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="33"/>
+      <c r="X10" s="33"/>
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="33"/>
+      <c r="AB10" s="33"/>
+      <c r="AC10" s="33"/>
+      <c r="AD10" s="33"/>
+      <c r="AE10" s="33"/>
+      <c r="AF10" s="33"/>
+      <c r="AG10" s="62"/>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>6</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -2030,7 +2009,7 @@
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="25" t="s">
         <v>157</v>
       </c>
       <c r="H11" s="8" t="s">
@@ -2046,106 +2025,106 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="29">
         <f t="shared" si="1"/>
         <v>46261</v>
       </c>
-      <c r="M11" s="30">
+      <c r="M11" s="29">
         <f t="shared" si="2"/>
         <v>46267</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="34"/>
-      <c r="W11" s="34"/>
-      <c r="X11" s="34"/>
-      <c r="Y11" s="34"/>
-      <c r="Z11" s="34"/>
-      <c r="AA11" s="34"/>
-      <c r="AB11" s="34"/>
-      <c r="AC11" s="34"/>
-      <c r="AD11" s="34"/>
-      <c r="AE11" s="34"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="81"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="33"/>
+      <c r="V11" s="33"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="33"/>
+      <c r="Y11" s="33"/>
+      <c r="Z11" s="33"/>
+      <c r="AA11" s="33"/>
+      <c r="AB11" s="33"/>
+      <c r="AC11" s="33"/>
+      <c r="AD11" s="33"/>
+      <c r="AE11" s="33"/>
+      <c r="AF11" s="33"/>
+      <c r="AG11" s="62"/>
     </row>
     <row r="12" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="42">
+      <c r="A12" s="40">
         <v>7</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="42" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="D12" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="44" t="s">
+      <c r="D12" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="H12" s="42" t="s">
+      <c r="H12" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="I12" s="42">
+      <c r="I12" s="40">
         <v>3</v>
       </c>
-      <c r="J12" s="42">
+      <c r="J12" s="40">
         <v>3</v>
       </c>
-      <c r="K12" s="42">
+      <c r="K12" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L12" s="46">
+      <c r="L12" s="43">
         <f t="shared" si="1"/>
         <v>46261</v>
       </c>
-      <c r="M12" s="46">
+      <c r="M12" s="43">
         <f t="shared" si="2"/>
         <v>46267</v>
       </c>
-      <c r="N12" s="42" t="s">
+      <c r="N12" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="47" t="s">
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
-      <c r="V12" s="34"/>
-      <c r="W12" s="34"/>
-      <c r="X12" s="34"/>
-      <c r="Y12" s="34"/>
-      <c r="Z12" s="34"/>
-      <c r="AA12" s="34"/>
-      <c r="AB12" s="34"/>
-      <c r="AC12" s="34"/>
-      <c r="AD12" s="34"/>
-      <c r="AE12" s="34"/>
-      <c r="AF12" s="34"/>
-      <c r="AG12" s="81"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="33"/>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="33"/>
+      <c r="Y12" s="33"/>
+      <c r="Z12" s="33"/>
+      <c r="AA12" s="33"/>
+      <c r="AB12" s="33"/>
+      <c r="AC12" s="33"/>
+      <c r="AD12" s="33"/>
+      <c r="AE12" s="33"/>
+      <c r="AF12" s="33"/>
+      <c r="AG12" s="62"/>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>8</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -2156,7 +2135,7 @@
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="25" t="s">
         <v>128</v>
       </c>
       <c r="H13" s="8" t="s">
@@ -2172,42 +2151,42 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="29">
         <f t="shared" si="1"/>
         <v>46261</v>
       </c>
-      <c r="M13" s="30">
+      <c r="M13" s="29">
         <f t="shared" si="2"/>
         <v>46274</v>
       </c>
       <c r="N13" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="34"/>
-      <c r="W13" s="34"/>
-      <c r="X13" s="34"/>
-      <c r="Y13" s="34"/>
-      <c r="Z13" s="34"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="34"/>
-      <c r="AC13" s="34"/>
-      <c r="AD13" s="34"/>
-      <c r="AE13" s="34"/>
-      <c r="AF13" s="34"/>
-      <c r="AG13" s="81"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="33"/>
+      <c r="T13" s="33"/>
+      <c r="U13" s="33"/>
+      <c r="V13" s="33"/>
+      <c r="W13" s="33"/>
+      <c r="X13" s="33"/>
+      <c r="Y13" s="33"/>
+      <c r="Z13" s="33"/>
+      <c r="AA13" s="33"/>
+      <c r="AB13" s="33"/>
+      <c r="AC13" s="33"/>
+      <c r="AD13" s="33"/>
+      <c r="AE13" s="33"/>
+      <c r="AF13" s="33"/>
+      <c r="AG13" s="62"/>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>9</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="9" t="s">
@@ -2218,7 +2197,7 @@
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="25" t="s">
         <v>128</v>
       </c>
       <c r="H14" s="8" t="s">
@@ -2234,106 +2213,106 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="29">
         <f t="shared" si="1"/>
         <v>46268</v>
       </c>
-      <c r="M14" s="30">
+      <c r="M14" s="29">
         <f t="shared" si="2"/>
         <v>46274</v>
       </c>
       <c r="N14" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="34"/>
-      <c r="W14" s="34"/>
-      <c r="X14" s="34"/>
-      <c r="Y14" s="34"/>
-      <c r="Z14" s="34"/>
-      <c r="AA14" s="34"/>
-      <c r="AB14" s="34"/>
-      <c r="AC14" s="34"/>
-      <c r="AD14" s="34"/>
-      <c r="AE14" s="34"/>
-      <c r="AF14" s="34"/>
-      <c r="AG14" s="81"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="33"/>
+      <c r="V14" s="33"/>
+      <c r="W14" s="33"/>
+      <c r="X14" s="33"/>
+      <c r="Y14" s="33"/>
+      <c r="Z14" s="33"/>
+      <c r="AA14" s="33"/>
+      <c r="AB14" s="33"/>
+      <c r="AC14" s="33"/>
+      <c r="AD14" s="33"/>
+      <c r="AE14" s="33"/>
+      <c r="AF14" s="33"/>
+      <c r="AG14" s="62"/>
     </row>
     <row r="15" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="42">
+      <c r="A15" s="40">
         <v>10</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="42" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="D15" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="44" t="s">
+      <c r="D15" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="H15" s="42" t="s">
+      <c r="H15" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="I15" s="42">
+      <c r="I15" s="40">
         <v>4</v>
       </c>
-      <c r="J15" s="42">
+      <c r="J15" s="40">
         <v>4</v>
       </c>
-      <c r="K15" s="42">
+      <c r="K15" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L15" s="46">
+      <c r="L15" s="43">
         <f t="shared" si="1"/>
         <v>46268</v>
       </c>
-      <c r="M15" s="46">
+      <c r="M15" s="43">
         <f t="shared" si="2"/>
         <v>46274</v>
       </c>
-      <c r="N15" s="42" t="s">
+      <c r="N15" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="47" t="s">
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="34"/>
-      <c r="W15" s="34"/>
-      <c r="X15" s="34"/>
-      <c r="Y15" s="34"/>
-      <c r="Z15" s="34"/>
-      <c r="AA15" s="34"/>
-      <c r="AB15" s="34"/>
-      <c r="AC15" s="34"/>
-      <c r="AD15" s="34"/>
-      <c r="AE15" s="34"/>
-      <c r="AF15" s="34"/>
-      <c r="AG15" s="81"/>
+      <c r="S15" s="33"/>
+      <c r="T15" s="33"/>
+      <c r="U15" s="33"/>
+      <c r="V15" s="33"/>
+      <c r="W15" s="33"/>
+      <c r="X15" s="33"/>
+      <c r="Y15" s="33"/>
+      <c r="Z15" s="33"/>
+      <c r="AA15" s="33"/>
+      <c r="AB15" s="33"/>
+      <c r="AC15" s="33"/>
+      <c r="AD15" s="33"/>
+      <c r="AE15" s="33"/>
+      <c r="AF15" s="33"/>
+      <c r="AG15" s="62"/>
     </row>
     <row r="16" spans="1:35" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>11</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="45" t="s">
         <v>48</v>
       </c>
       <c r="C16" s="20" t="s">
@@ -2344,7 +2323,7 @@
         <v>32</v>
       </c>
       <c r="F16" s="21"/>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="45" t="s">
         <v>128</v>
       </c>
       <c r="H16" s="19" t="s">
@@ -2360,36 +2339,36 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L16" s="50">
+      <c r="L16" s="46">
         <f t="shared" si="1"/>
         <v>46268</v>
       </c>
-      <c r="M16" s="50">
+      <c r="M16" s="46">
         <f t="shared" si="2"/>
         <v>46281</v>
       </c>
       <c r="N16" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="51"/>
-      <c r="S16" s="51"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="34"/>
-      <c r="W16" s="34"/>
-      <c r="X16" s="34"/>
-      <c r="Y16" s="34"/>
-      <c r="Z16" s="34"/>
-      <c r="AA16" s="34"/>
-      <c r="AB16" s="34"/>
-      <c r="AC16" s="34"/>
-      <c r="AD16" s="34"/>
-      <c r="AE16" s="34"/>
-      <c r="AF16" s="34"/>
-      <c r="AG16" s="52" t="s">
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="47"/>
+      <c r="S16" s="47"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="33"/>
+      <c r="AB16" s="33"/>
+      <c r="AC16" s="33"/>
+      <c r="AD16" s="33"/>
+      <c r="AE16" s="33"/>
+      <c r="AF16" s="33"/>
+      <c r="AG16" s="48" t="s">
         <v>181</v>
       </c>
     </row>
@@ -2397,7 +2376,7 @@
       <c r="A17" s="19">
         <v>12</v>
       </c>
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="45" t="s">
         <v>48</v>
       </c>
       <c r="C17" s="20" t="s">
@@ -2408,7 +2387,7 @@
         <v>32</v>
       </c>
       <c r="F17" s="21"/>
-      <c r="G17" s="48" t="s">
+      <c r="G17" s="45" t="s">
         <v>182</v>
       </c>
       <c r="H17" s="19" t="s">
@@ -2424,36 +2403,36 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L17" s="50">
+      <c r="L17" s="46">
         <f t="shared" si="1"/>
         <v>46268</v>
       </c>
-      <c r="M17" s="50">
+      <c r="M17" s="46">
         <f t="shared" si="2"/>
         <v>46281</v>
       </c>
       <c r="N17" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="51"/>
-      <c r="S17" s="51"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="34"/>
-      <c r="W17" s="34"/>
-      <c r="X17" s="34"/>
-      <c r="Y17" s="34"/>
-      <c r="Z17" s="34"/>
-      <c r="AA17" s="34"/>
-      <c r="AB17" s="34"/>
-      <c r="AC17" s="34"/>
-      <c r="AD17" s="34"/>
-      <c r="AE17" s="34"/>
-      <c r="AF17" s="34"/>
-      <c r="AG17" s="52" t="s">
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="33"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="33"/>
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="33"/>
+      <c r="AA17" s="33"/>
+      <c r="AB17" s="33"/>
+      <c r="AC17" s="33"/>
+      <c r="AD17" s="33"/>
+      <c r="AE17" s="33"/>
+      <c r="AF17" s="33"/>
+      <c r="AG17" s="48" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2461,7 +2440,7 @@
       <c r="A18" s="19">
         <v>13</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="45" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="20" t="s">
@@ -2472,7 +2451,7 @@
         <v>32</v>
       </c>
       <c r="F18" s="21"/>
-      <c r="G18" s="48" t="s">
+      <c r="G18" s="45" t="s">
         <v>159</v>
       </c>
       <c r="H18" s="19" t="s">
@@ -2488,36 +2467,36 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L18" s="50">
+      <c r="L18" s="46">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="M18" s="50">
+      <c r="M18" s="46">
         <f t="shared" si="2"/>
         <v>46288</v>
       </c>
       <c r="N18" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="51"/>
-      <c r="T18" s="51"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="34"/>
-      <c r="W18" s="34"/>
-      <c r="X18" s="34"/>
-      <c r="Y18" s="34"/>
-      <c r="Z18" s="34"/>
-      <c r="AA18" s="34"/>
-      <c r="AB18" s="34"/>
-      <c r="AC18" s="34"/>
-      <c r="AD18" s="34"/>
-      <c r="AE18" s="34"/>
-      <c r="AF18" s="34"/>
-      <c r="AG18" s="52" t="s">
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="47"/>
+      <c r="T18" s="47"/>
+      <c r="U18" s="33"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="33"/>
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="33"/>
+      <c r="AA18" s="33"/>
+      <c r="AB18" s="33"/>
+      <c r="AC18" s="33"/>
+      <c r="AD18" s="33"/>
+      <c r="AE18" s="33"/>
+      <c r="AF18" s="33"/>
+      <c r="AG18" s="48" t="s">
         <v>184</v>
       </c>
     </row>
@@ -2525,7 +2504,7 @@
       <c r="A19" s="19">
         <v>14</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="45" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="20" t="s">
@@ -2536,7 +2515,7 @@
         <v>32</v>
       </c>
       <c r="F19" s="21"/>
-      <c r="G19" s="48" t="s">
+      <c r="G19" s="45" t="s">
         <v>182</v>
       </c>
       <c r="H19" s="19" t="s">
@@ -2552,36 +2531,36 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L19" s="50">
+      <c r="L19" s="46">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="M19" s="50">
+      <c r="M19" s="46">
         <f t="shared" si="2"/>
         <v>46288</v>
       </c>
       <c r="N19" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="51"/>
-      <c r="T19" s="51"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="34"/>
-      <c r="W19" s="34"/>
-      <c r="X19" s="34"/>
-      <c r="Y19" s="34"/>
-      <c r="Z19" s="34"/>
-      <c r="AA19" s="34"/>
-      <c r="AB19" s="34"/>
-      <c r="AC19" s="34"/>
-      <c r="AD19" s="34"/>
-      <c r="AE19" s="34"/>
-      <c r="AF19" s="34"/>
-      <c r="AG19" s="52" t="s">
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="33"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="33"/>
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="33"/>
+      <c r="AA19" s="33"/>
+      <c r="AB19" s="33"/>
+      <c r="AC19" s="33"/>
+      <c r="AD19" s="33"/>
+      <c r="AE19" s="33"/>
+      <c r="AF19" s="33"/>
+      <c r="AG19" s="48" t="s">
         <v>185</v>
       </c>
     </row>
@@ -2589,7 +2568,7 @@
       <c r="A20" s="19">
         <v>15</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="45" t="s">
         <v>48</v>
       </c>
       <c r="C20" s="20" t="s">
@@ -2600,7 +2579,7 @@
         <v>32</v>
       </c>
       <c r="F20" s="21"/>
-      <c r="G20" s="48" t="s">
+      <c r="G20" s="45" t="s">
         <v>157</v>
       </c>
       <c r="H20" s="19" t="s">
@@ -2616,102 +2595,102 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L20" s="50">
+      <c r="L20" s="46">
         <f t="shared" si="1"/>
         <v>46282</v>
       </c>
-      <c r="M20" s="50">
+      <c r="M20" s="46">
         <f t="shared" si="2"/>
         <v>46288</v>
       </c>
       <c r="N20" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="51"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="34"/>
-      <c r="W20" s="34"/>
-      <c r="X20" s="34"/>
-      <c r="Y20" s="34"/>
-      <c r="Z20" s="34"/>
-      <c r="AA20" s="34"/>
-      <c r="AB20" s="34"/>
-      <c r="AC20" s="34"/>
-      <c r="AD20" s="34"/>
-      <c r="AE20" s="34"/>
-      <c r="AF20" s="34"/>
-      <c r="AG20" s="52" t="s">
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="33"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="33"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="33"/>
+      <c r="V20" s="33"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="33"/>
+      <c r="Y20" s="33"/>
+      <c r="Z20" s="33"/>
+      <c r="AA20" s="33"/>
+      <c r="AB20" s="33"/>
+      <c r="AC20" s="33"/>
+      <c r="AD20" s="33"/>
+      <c r="AE20" s="33"/>
+      <c r="AF20" s="33"/>
+      <c r="AG20" s="48" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:33" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="42">
+      <c r="A21" s="40">
         <v>16</v>
       </c>
-      <c r="B21" s="44" t="s">
+      <c r="B21" s="42" t="s">
         <v>48</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="42"/>
-      <c r="G21" s="44" t="s">
+      <c r="D21" s="40"/>
+      <c r="E21" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="40"/>
+      <c r="G21" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="H21" s="42" t="s">
+      <c r="H21" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="I21" s="42">
+      <c r="I21" s="40">
         <v>6</v>
       </c>
-      <c r="J21" s="42">
+      <c r="J21" s="40">
         <v>6</v>
       </c>
-      <c r="K21" s="42">
+      <c r="K21" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L21" s="46">
+      <c r="L21" s="43">
         <f t="shared" si="1"/>
         <v>46282</v>
       </c>
-      <c r="M21" s="46">
+      <c r="M21" s="43">
         <f t="shared" si="2"/>
         <v>46288</v>
       </c>
-      <c r="N21" s="42" t="s">
+      <c r="N21" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="47" t="s">
+      <c r="O21" s="33"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="33"/>
+      <c r="T21" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="U21" s="34"/>
-      <c r="V21" s="34"/>
-      <c r="W21" s="34"/>
-      <c r="X21" s="34"/>
-      <c r="Y21" s="34"/>
-      <c r="Z21" s="34"/>
-      <c r="AA21" s="34"/>
-      <c r="AB21" s="34"/>
-      <c r="AC21" s="34"/>
-      <c r="AD21" s="34"/>
-      <c r="AE21" s="34"/>
-      <c r="AF21" s="34"/>
-      <c r="AG21" s="52" t="s">
+      <c r="U21" s="33"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="33"/>
+      <c r="AB21" s="33"/>
+      <c r="AC21" s="33"/>
+      <c r="AD21" s="33"/>
+      <c r="AE21" s="33"/>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="48" t="s">
         <v>189</v>
       </c>
     </row>
@@ -2746,36 +2725,36 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L22" s="54">
+      <c r="L22" s="49">
         <f t="shared" si="1"/>
         <v>46289</v>
       </c>
-      <c r="M22" s="54">
+      <c r="M22" s="49">
         <f t="shared" si="2"/>
         <v>46295</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O22" s="34"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="51"/>
-      <c r="V22" s="34"/>
-      <c r="W22" s="34"/>
-      <c r="X22" s="34"/>
-      <c r="Y22" s="34"/>
-      <c r="Z22" s="34"/>
-      <c r="AA22" s="34"/>
-      <c r="AB22" s="34"/>
-      <c r="AC22" s="34"/>
-      <c r="AD22" s="34"/>
-      <c r="AE22" s="34"/>
-      <c r="AF22" s="34"/>
-      <c r="AG22" s="81"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="33"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="47"/>
+      <c r="V22" s="33"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="33"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="33"/>
+      <c r="AA22" s="33"/>
+      <c r="AB22" s="33"/>
+      <c r="AC22" s="33"/>
+      <c r="AD22" s="33"/>
+      <c r="AE22" s="33"/>
+      <c r="AF22" s="33"/>
+      <c r="AG22" s="62"/>
     </row>
     <row r="23" spans="1:33" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -2808,36 +2787,36 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L23" s="54">
+      <c r="L23" s="49">
         <f t="shared" si="1"/>
         <v>46289</v>
       </c>
-      <c r="M23" s="54">
+      <c r="M23" s="49">
         <f t="shared" si="2"/>
         <v>46302</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
-      <c r="S23" s="34"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="56"/>
-      <c r="V23" s="56"/>
-      <c r="W23" s="34"/>
-      <c r="X23" s="34"/>
-      <c r="Y23" s="34"/>
-      <c r="Z23" s="34"/>
-      <c r="AA23" s="34"/>
-      <c r="AB23" s="34"/>
-      <c r="AC23" s="34"/>
-      <c r="AD23" s="34"/>
-      <c r="AE23" s="34"/>
-      <c r="AF23" s="34"/>
-      <c r="AG23" s="52" t="s">
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="33"/>
+      <c r="S23" s="33"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="50"/>
+      <c r="V23" s="50"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="33"/>
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="33"/>
+      <c r="AA23" s="33"/>
+      <c r="AB23" s="33"/>
+      <c r="AC23" s="33"/>
+      <c r="AD23" s="33"/>
+      <c r="AE23" s="33"/>
+      <c r="AF23" s="33"/>
+      <c r="AG23" s="48" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2872,36 +2851,36 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L24" s="54">
+      <c r="L24" s="49">
         <f t="shared" si="1"/>
         <v>46289</v>
       </c>
-      <c r="M24" s="54">
+      <c r="M24" s="49">
         <f t="shared" si="2"/>
         <v>46302</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34"/>
-      <c r="S24" s="34"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="51"/>
-      <c r="V24" s="51"/>
-      <c r="W24" s="34"/>
-      <c r="X24" s="34"/>
-      <c r="Y24" s="34"/>
-      <c r="Z24" s="34"/>
-      <c r="AA24" s="34"/>
-      <c r="AB24" s="34"/>
-      <c r="AC24" s="34"/>
-      <c r="AD24" s="34"/>
-      <c r="AE24" s="34"/>
-      <c r="AF24" s="34"/>
-      <c r="AG24" s="52" t="s">
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="33"/>
+      <c r="S24" s="33"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="47"/>
+      <c r="V24" s="47"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="33"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="33"/>
+      <c r="AA24" s="33"/>
+      <c r="AB24" s="33"/>
+      <c r="AC24" s="33"/>
+      <c r="AD24" s="33"/>
+      <c r="AE24" s="33"/>
+      <c r="AF24" s="33"/>
+      <c r="AG24" s="48" t="s">
         <v>192</v>
       </c>
     </row>
@@ -2936,36 +2915,36 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L25" s="54">
+      <c r="L25" s="49">
         <f t="shared" si="1"/>
         <v>46296</v>
       </c>
-      <c r="M25" s="54">
+      <c r="M25" s="49">
         <f t="shared" si="2"/>
         <v>46309</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="34"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="34"/>
-      <c r="V25" s="56"/>
-      <c r="W25" s="56"/>
-      <c r="X25" s="34"/>
-      <c r="Y25" s="34"/>
-      <c r="Z25" s="34"/>
-      <c r="AA25" s="34"/>
-      <c r="AB25" s="34"/>
-      <c r="AC25" s="34"/>
-      <c r="AD25" s="34"/>
-      <c r="AE25" s="34"/>
-      <c r="AF25" s="34"/>
-      <c r="AG25" s="52" t="s">
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
+      <c r="S25" s="33"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="33"/>
+      <c r="V25" s="50"/>
+      <c r="W25" s="50"/>
+      <c r="X25" s="33"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="33"/>
+      <c r="AC25" s="33"/>
+      <c r="AD25" s="33"/>
+      <c r="AE25" s="33"/>
+      <c r="AF25" s="33"/>
+      <c r="AG25" s="48" t="s">
         <v>193</v>
       </c>
     </row>
@@ -3000,36 +2979,36 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L26" s="54">
+      <c r="L26" s="49">
         <f t="shared" si="1"/>
         <v>46296</v>
       </c>
-      <c r="M26" s="54">
+      <c r="M26" s="49">
         <f t="shared" si="2"/>
         <v>46309</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O26" s="34"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="34"/>
-      <c r="S26" s="34"/>
-      <c r="T26" s="34"/>
-      <c r="U26" s="34"/>
-      <c r="V26" s="51"/>
-      <c r="W26" s="51"/>
-      <c r="X26" s="34"/>
-      <c r="Y26" s="34"/>
-      <c r="Z26" s="34"/>
-      <c r="AA26" s="34"/>
-      <c r="AB26" s="34"/>
-      <c r="AC26" s="34"/>
-      <c r="AD26" s="34"/>
-      <c r="AE26" s="34"/>
-      <c r="AF26" s="34"/>
-      <c r="AG26" s="81"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="33"/>
+      <c r="S26" s="33"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="33"/>
+      <c r="V26" s="47"/>
+      <c r="W26" s="47"/>
+      <c r="X26" s="33"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33"/>
+      <c r="AA26" s="33"/>
+      <c r="AB26" s="33"/>
+      <c r="AC26" s="33"/>
+      <c r="AD26" s="33"/>
+      <c r="AE26" s="33"/>
+      <c r="AF26" s="33"/>
+      <c r="AG26" s="62"/>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -3062,1468 +3041,1468 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L27" s="54">
+      <c r="L27" s="49">
         <f t="shared" si="1"/>
         <v>46303</v>
       </c>
-      <c r="M27" s="54">
+      <c r="M27" s="49">
         <f t="shared" si="2"/>
         <v>46309</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="O27" s="34"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="34"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="34"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="34"/>
-      <c r="V27" s="34"/>
-      <c r="W27" s="51"/>
-      <c r="X27" s="34"/>
-      <c r="Y27" s="34"/>
-      <c r="Z27" s="34"/>
-      <c r="AA27" s="34"/>
-      <c r="AB27" s="34"/>
-      <c r="AC27" s="34"/>
-      <c r="AD27" s="34"/>
-      <c r="AE27" s="34"/>
-      <c r="AF27" s="34"/>
-      <c r="AG27" s="52" t="s">
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
+      <c r="AC27" s="33"/>
+      <c r="AD27" s="33"/>
+      <c r="AE27" s="33"/>
+      <c r="AF27" s="33"/>
+      <c r="AG27" s="48" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:33" ht="24" x14ac:dyDescent="0.25">
-      <c r="A28" s="42">
+      <c r="A28" s="40">
         <v>23</v>
       </c>
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="42" t="s">
         <v>55</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="42"/>
-      <c r="G28" s="44" t="s">
+      <c r="D28" s="40"/>
+      <c r="E28" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="40"/>
+      <c r="G28" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="H28" s="42" t="s">
+      <c r="H28" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="I28" s="42">
+      <c r="I28" s="40">
         <v>9</v>
       </c>
-      <c r="J28" s="42">
+      <c r="J28" s="40">
         <v>9</v>
       </c>
-      <c r="K28" s="42">
+      <c r="K28" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L28" s="46">
+      <c r="L28" s="43">
         <f t="shared" si="1"/>
         <v>46303</v>
       </c>
-      <c r="M28" s="46">
+      <c r="M28" s="43">
         <f t="shared" si="2"/>
         <v>46309</v>
       </c>
-      <c r="N28" s="42" t="s">
+      <c r="N28" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="34"/>
-      <c r="V28" s="34"/>
-      <c r="W28" s="47" t="s">
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="33"/>
+      <c r="S28" s="33"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="X28" s="34"/>
-      <c r="Y28" s="34"/>
-      <c r="Z28" s="34"/>
-      <c r="AA28" s="34"/>
-      <c r="AB28" s="34"/>
-      <c r="AC28" s="34"/>
-      <c r="AD28" s="34"/>
-      <c r="AE28" s="34"/>
-      <c r="AF28" s="34"/>
-      <c r="AG28" s="52" t="s">
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
+      <c r="AA28" s="33"/>
+      <c r="AB28" s="33"/>
+      <c r="AC28" s="33"/>
+      <c r="AD28" s="33"/>
+      <c r="AE28" s="33"/>
+      <c r="AF28" s="33"/>
+      <c r="AG28" s="48" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" s="27">
+      <c r="A29" s="26">
         <v>24</v>
       </c>
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" s="29"/>
-      <c r="G29" s="58" t="s">
+      <c r="D29" s="28"/>
+      <c r="E29" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" s="28"/>
+      <c r="G29" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="H29" s="27" t="s">
+      <c r="H29" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="26">
         <v>10</v>
       </c>
-      <c r="J29" s="27">
+      <c r="J29" s="26">
         <v>10</v>
       </c>
-      <c r="K29" s="27">
+      <c r="K29" s="26">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L29" s="59">
+      <c r="L29" s="52">
         <f t="shared" si="1"/>
         <v>46310</v>
       </c>
-      <c r="M29" s="59">
+      <c r="M29" s="52">
         <f t="shared" si="2"/>
         <v>46316</v>
       </c>
-      <c r="N29" s="27" t="s">
+      <c r="N29" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="O29" s="34"/>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="34"/>
-      <c r="R29" s="34"/>
-      <c r="S29" s="34"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="34"/>
-      <c r="V29" s="34"/>
-      <c r="W29" s="34"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="34"/>
-      <c r="Z29" s="34"/>
-      <c r="AA29" s="34"/>
-      <c r="AB29" s="34"/>
-      <c r="AC29" s="34"/>
-      <c r="AD29" s="34"/>
-      <c r="AE29" s="34"/>
-      <c r="AF29" s="34"/>
-      <c r="AG29" s="52" t="s">
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="33"/>
+      <c r="S29" s="33"/>
+      <c r="T29" s="33"/>
+      <c r="U29" s="33"/>
+      <c r="V29" s="33"/>
+      <c r="W29" s="33"/>
+      <c r="X29" s="34"/>
+      <c r="Y29" s="33"/>
+      <c r="Z29" s="33"/>
+      <c r="AA29" s="33"/>
+      <c r="AB29" s="33"/>
+      <c r="AC29" s="33"/>
+      <c r="AD29" s="33"/>
+      <c r="AE29" s="33"/>
+      <c r="AF29" s="33"/>
+      <c r="AG29" s="48" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:33" ht="24" x14ac:dyDescent="0.25">
-      <c r="A30" s="27">
+      <c r="A30" s="26">
         <v>25</v>
       </c>
-      <c r="B30" s="58" t="s">
+      <c r="B30" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="29"/>
-      <c r="G30" s="58" t="s">
+      <c r="D30" s="28"/>
+      <c r="E30" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="28"/>
+      <c r="G30" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="H30" s="27" t="s">
+      <c r="H30" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="26">
         <v>10</v>
       </c>
-      <c r="J30" s="27">
+      <c r="J30" s="26">
         <v>11</v>
       </c>
-      <c r="K30" s="27">
+      <c r="K30" s="26">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L30" s="59">
+      <c r="L30" s="52">
         <f t="shared" si="1"/>
         <v>46310</v>
       </c>
-      <c r="M30" s="59">
+      <c r="M30" s="52">
         <f t="shared" si="2"/>
         <v>46323</v>
       </c>
-      <c r="N30" s="27" t="s">
+      <c r="N30" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="34"/>
-      <c r="V30" s="34"/>
-      <c r="W30" s="34"/>
-      <c r="X30" s="56"/>
-      <c r="Y30" s="56"/>
-      <c r="Z30" s="34"/>
-      <c r="AA30" s="34"/>
-      <c r="AB30" s="34"/>
-      <c r="AC30" s="34"/>
-      <c r="AD30" s="34"/>
-      <c r="AE30" s="34"/>
-      <c r="AF30" s="34"/>
-      <c r="AG30" s="52" t="s">
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="33"/>
+      <c r="S30" s="33"/>
+      <c r="T30" s="33"/>
+      <c r="U30" s="33"/>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="50"/>
+      <c r="Y30" s="50"/>
+      <c r="Z30" s="33"/>
+      <c r="AA30" s="33"/>
+      <c r="AB30" s="33"/>
+      <c r="AC30" s="33"/>
+      <c r="AD30" s="33"/>
+      <c r="AE30" s="33"/>
+      <c r="AF30" s="33"/>
+      <c r="AG30" s="48" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="24" x14ac:dyDescent="0.25">
-      <c r="A31" s="27">
+      <c r="A31" s="26">
         <v>26</v>
       </c>
-      <c r="B31" s="58" t="s">
+      <c r="B31" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="29"/>
-      <c r="G31" s="58" t="s">
+      <c r="D31" s="28"/>
+      <c r="E31" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" s="28"/>
+      <c r="G31" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="H31" s="27" t="s">
+      <c r="H31" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="I31" s="27">
+      <c r="I31" s="26">
         <v>11</v>
       </c>
-      <c r="J31" s="27">
+      <c r="J31" s="26">
         <v>12</v>
       </c>
-      <c r="K31" s="27">
+      <c r="K31" s="26">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L31" s="59">
+      <c r="L31" s="52">
         <f t="shared" si="1"/>
         <v>46317</v>
       </c>
-      <c r="M31" s="59">
+      <c r="M31" s="52">
         <f t="shared" si="2"/>
         <v>46330</v>
       </c>
-      <c r="N31" s="27" t="s">
+      <c r="N31" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="O31" s="34"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="34"/>
-      <c r="V31" s="34"/>
-      <c r="W31" s="34"/>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="56"/>
-      <c r="Z31" s="56"/>
-      <c r="AA31" s="34"/>
-      <c r="AB31" s="34"/>
-      <c r="AC31" s="34"/>
-      <c r="AD31" s="34"/>
-      <c r="AE31" s="34"/>
-      <c r="AF31" s="34"/>
-      <c r="AG31" s="52" t="s">
+      <c r="O31" s="33"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="33"/>
+      <c r="S31" s="33"/>
+      <c r="T31" s="33"/>
+      <c r="U31" s="33"/>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
+      <c r="X31" s="33"/>
+      <c r="Y31" s="50"/>
+      <c r="Z31" s="50"/>
+      <c r="AA31" s="33"/>
+      <c r="AB31" s="33"/>
+      <c r="AC31" s="33"/>
+      <c r="AD31" s="33"/>
+      <c r="AE31" s="33"/>
+      <c r="AF31" s="33"/>
+      <c r="AG31" s="48" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="32" spans="1:33" ht="24" x14ac:dyDescent="0.25">
-      <c r="A32" s="27">
+      <c r="A32" s="26">
         <v>27</v>
       </c>
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="29"/>
-      <c r="G32" s="58" t="s">
+      <c r="D32" s="28"/>
+      <c r="E32" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" s="28"/>
+      <c r="G32" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="H32" s="27" t="s">
+      <c r="H32" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="26">
         <v>12</v>
       </c>
-      <c r="J32" s="27">
+      <c r="J32" s="26">
         <v>12</v>
       </c>
-      <c r="K32" s="27">
+      <c r="K32" s="26">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L32" s="59">
+      <c r="L32" s="52">
         <f t="shared" si="1"/>
         <v>46324</v>
       </c>
-      <c r="M32" s="59">
+      <c r="M32" s="52">
         <f t="shared" si="2"/>
         <v>46330</v>
       </c>
-      <c r="N32" s="27" t="s">
+      <c r="N32" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="O32" s="34"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="34"/>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-      <c r="U32" s="34"/>
-      <c r="V32" s="34"/>
-      <c r="W32" s="34"/>
-      <c r="X32" s="34"/>
-      <c r="Y32" s="34"/>
-      <c r="Z32" s="56"/>
-      <c r="AA32" s="34"/>
-      <c r="AB32" s="34"/>
-      <c r="AC32" s="34"/>
-      <c r="AD32" s="34"/>
-      <c r="AE32" s="34"/>
-      <c r="AF32" s="34"/>
-      <c r="AG32" s="52" t="s">
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="33"/>
+      <c r="S32" s="33"/>
+      <c r="T32" s="33"/>
+      <c r="U32" s="33"/>
+      <c r="V32" s="33"/>
+      <c r="W32" s="33"/>
+      <c r="X32" s="33"/>
+      <c r="Y32" s="33"/>
+      <c r="Z32" s="50"/>
+      <c r="AA32" s="33"/>
+      <c r="AB32" s="33"/>
+      <c r="AC32" s="33"/>
+      <c r="AD32" s="33"/>
+      <c r="AE32" s="33"/>
+      <c r="AF32" s="33"/>
+      <c r="AG32" s="48" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A33" s="27">
+      <c r="A33" s="26">
         <v>28</v>
       </c>
-      <c r="B33" s="58" t="s">
+      <c r="B33" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F33" s="29"/>
-      <c r="G33" s="58" t="s">
+      <c r="D33" s="28"/>
+      <c r="E33" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" s="28"/>
+      <c r="G33" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="H33" s="27" t="s">
+      <c r="H33" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="26">
         <v>12</v>
       </c>
-      <c r="J33" s="27">
+      <c r="J33" s="26">
         <v>13</v>
       </c>
-      <c r="K33" s="27">
+      <c r="K33" s="26">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L33" s="59">
+      <c r="L33" s="52">
         <f t="shared" si="1"/>
         <v>46324</v>
       </c>
-      <c r="M33" s="59">
+      <c r="M33" s="52">
         <f t="shared" si="2"/>
         <v>46337</v>
       </c>
-      <c r="N33" s="27" t="s">
+      <c r="N33" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="U33" s="34"/>
-      <c r="V33" s="34"/>
-      <c r="W33" s="34"/>
-      <c r="X33" s="34"/>
-      <c r="Y33" s="34"/>
-      <c r="Z33" s="51"/>
-      <c r="AA33" s="51"/>
-      <c r="AB33" s="34"/>
-      <c r="AC33" s="34"/>
-      <c r="AD33" s="34"/>
-      <c r="AE33" s="34"/>
-      <c r="AF33" s="34"/>
-      <c r="AG33" s="52" t="s">
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="33"/>
+      <c r="S33" s="33"/>
+      <c r="T33" s="33"/>
+      <c r="U33" s="33"/>
+      <c r="V33" s="33"/>
+      <c r="W33" s="33"/>
+      <c r="X33" s="33"/>
+      <c r="Y33" s="33"/>
+      <c r="Z33" s="47"/>
+      <c r="AA33" s="47"/>
+      <c r="AB33" s="33"/>
+      <c r="AC33" s="33"/>
+      <c r="AD33" s="33"/>
+      <c r="AE33" s="33"/>
+      <c r="AF33" s="33"/>
+      <c r="AG33" s="48" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:33" ht="24" x14ac:dyDescent="0.25">
-      <c r="A34" s="27">
+      <c r="A34" s="26">
         <v>29</v>
       </c>
-      <c r="B34" s="58" t="s">
+      <c r="B34" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" s="29"/>
-      <c r="G34" s="58" t="s">
+      <c r="D34" s="28"/>
+      <c r="E34" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" s="28"/>
+      <c r="G34" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="H34" s="27" t="s">
+      <c r="H34" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="26">
         <v>13</v>
       </c>
-      <c r="J34" s="27">
+      <c r="J34" s="26">
         <v>13</v>
       </c>
-      <c r="K34" s="27">
+      <c r="K34" s="26">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L34" s="59">
+      <c r="L34" s="52">
         <f t="shared" si="1"/>
         <v>46331</v>
       </c>
-      <c r="M34" s="59">
+      <c r="M34" s="52">
         <f t="shared" si="2"/>
         <v>46337</v>
       </c>
-      <c r="N34" s="27" t="s">
+      <c r="N34" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="34"/>
-      <c r="W34" s="34"/>
-      <c r="X34" s="34"/>
-      <c r="Y34" s="34"/>
-      <c r="Z34" s="34"/>
-      <c r="AA34" s="56"/>
-      <c r="AB34" s="34"/>
-      <c r="AC34" s="34"/>
-      <c r="AD34" s="34"/>
-      <c r="AE34" s="34"/>
-      <c r="AF34" s="34"/>
-      <c r="AG34" s="52" t="s">
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="33"/>
+      <c r="S34" s="33"/>
+      <c r="T34" s="33"/>
+      <c r="U34" s="33"/>
+      <c r="V34" s="33"/>
+      <c r="W34" s="33"/>
+      <c r="X34" s="33"/>
+      <c r="Y34" s="33"/>
+      <c r="Z34" s="33"/>
+      <c r="AA34" s="50"/>
+      <c r="AB34" s="33"/>
+      <c r="AC34" s="33"/>
+      <c r="AD34" s="33"/>
+      <c r="AE34" s="33"/>
+      <c r="AF34" s="33"/>
+      <c r="AG34" s="48" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="35" spans="1:33" ht="24" x14ac:dyDescent="0.25">
-      <c r="A35" s="42">
+      <c r="A35" s="40">
         <v>30</v>
       </c>
-      <c r="B35" s="44" t="s">
+      <c r="B35" s="42" t="s">
         <v>66</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F35" s="42"/>
-      <c r="G35" s="44" t="s">
+      <c r="D35" s="40"/>
+      <c r="E35" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" s="40"/>
+      <c r="G35" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="H35" s="42" t="s">
+      <c r="H35" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="I35" s="42">
+      <c r="I35" s="40">
         <v>13</v>
       </c>
-      <c r="J35" s="42">
+      <c r="J35" s="40">
         <v>13</v>
       </c>
-      <c r="K35" s="42">
+      <c r="K35" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L35" s="46">
+      <c r="L35" s="43">
         <f t="shared" si="1"/>
         <v>46331</v>
       </c>
-      <c r="M35" s="46">
+      <c r="M35" s="43">
         <f t="shared" si="2"/>
         <v>46337</v>
       </c>
-      <c r="N35" s="42" t="s">
+      <c r="N35" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="34"/>
-      <c r="T35" s="34"/>
-      <c r="U35" s="34"/>
-      <c r="V35" s="34"/>
-      <c r="W35" s="34"/>
-      <c r="X35" s="34"/>
-      <c r="Y35" s="34"/>
-      <c r="Z35" s="34"/>
-      <c r="AA35" s="47" t="s">
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
+      <c r="S35" s="33"/>
+      <c r="T35" s="33"/>
+      <c r="U35" s="33"/>
+      <c r="V35" s="33"/>
+      <c r="W35" s="33"/>
+      <c r="X35" s="33"/>
+      <c r="Y35" s="33"/>
+      <c r="Z35" s="33"/>
+      <c r="AA35" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="AB35" s="34"/>
-      <c r="AC35" s="34"/>
-      <c r="AD35" s="34"/>
-      <c r="AE35" s="34"/>
-      <c r="AF35" s="34"/>
-      <c r="AG35" s="52" t="s">
+      <c r="AB35" s="33"/>
+      <c r="AC35" s="33"/>
+      <c r="AD35" s="33"/>
+      <c r="AE35" s="33"/>
+      <c r="AF35" s="33"/>
+      <c r="AG35" s="48" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="31">
+      <c r="A36" s="30">
         <v>31</v>
       </c>
-      <c r="B36" s="60" t="s">
+      <c r="B36" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="F36" s="33"/>
-      <c r="G36" s="60" t="s">
+      <c r="D36" s="32"/>
+      <c r="E36" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F36" s="32"/>
+      <c r="G36" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="H36" s="31" t="s">
+      <c r="H36" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="I36" s="31">
+      <c r="I36" s="30">
         <v>14</v>
       </c>
-      <c r="J36" s="31">
+      <c r="J36" s="30">
         <v>14</v>
       </c>
-      <c r="K36" s="31">
+      <c r="K36" s="30">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L36" s="61">
+      <c r="L36" s="54">
         <f t="shared" si="1"/>
         <v>46338</v>
       </c>
-      <c r="M36" s="61">
+      <c r="M36" s="54">
         <f t="shared" si="2"/>
         <v>46344</v>
       </c>
-      <c r="N36" s="31" t="s">
+      <c r="N36" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="34"/>
-      <c r="V36" s="34"/>
-      <c r="W36" s="34"/>
-      <c r="X36" s="34"/>
-      <c r="Y36" s="34"/>
-      <c r="Z36" s="34"/>
-      <c r="AA36" s="34"/>
-      <c r="AB36" s="51"/>
-      <c r="AC36" s="34"/>
-      <c r="AD36" s="34"/>
-      <c r="AE36" s="34"/>
-      <c r="AF36" s="34"/>
-      <c r="AG36" s="81"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="33"/>
+      <c r="S36" s="33"/>
+      <c r="T36" s="33"/>
+      <c r="U36" s="33"/>
+      <c r="V36" s="33"/>
+      <c r="W36" s="33"/>
+      <c r="X36" s="33"/>
+      <c r="Y36" s="33"/>
+      <c r="Z36" s="33"/>
+      <c r="AA36" s="33"/>
+      <c r="AB36" s="47"/>
+      <c r="AC36" s="33"/>
+      <c r="AD36" s="33"/>
+      <c r="AE36" s="33"/>
+      <c r="AF36" s="33"/>
+      <c r="AG36" s="62"/>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" s="31">
-        <v>32</v>
-      </c>
-      <c r="B37" s="60" t="s">
+      <c r="A37" s="30">
+        <v>32</v>
+      </c>
+      <c r="B37" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" s="33"/>
-      <c r="G37" s="60" t="s">
+      <c r="D37" s="32"/>
+      <c r="E37" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" s="32"/>
+      <c r="G37" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="H37" s="31" t="s">
+      <c r="H37" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="I37" s="31">
+      <c r="I37" s="30">
         <v>14</v>
       </c>
-      <c r="J37" s="31">
+      <c r="J37" s="30">
         <v>15</v>
       </c>
-      <c r="K37" s="31">
+      <c r="K37" s="30">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L37" s="61">
+      <c r="L37" s="54">
         <f t="shared" si="1"/>
         <v>46338</v>
       </c>
-      <c r="M37" s="61">
+      <c r="M37" s="54">
         <f t="shared" si="2"/>
         <v>46351</v>
       </c>
-      <c r="N37" s="31" t="s">
+      <c r="N37" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="34"/>
-      <c r="T37" s="34"/>
-      <c r="U37" s="34"/>
-      <c r="V37" s="34"/>
-      <c r="W37" s="34"/>
-      <c r="X37" s="34"/>
-      <c r="Y37" s="34"/>
-      <c r="Z37" s="34"/>
-      <c r="AA37" s="34"/>
-      <c r="AB37" s="51"/>
-      <c r="AC37" s="51"/>
-      <c r="AD37" s="34"/>
-      <c r="AE37" s="34"/>
-      <c r="AF37" s="34"/>
-      <c r="AG37" s="81"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="33"/>
+      <c r="S37" s="33"/>
+      <c r="T37" s="33"/>
+      <c r="U37" s="33"/>
+      <c r="V37" s="33"/>
+      <c r="W37" s="33"/>
+      <c r="X37" s="33"/>
+      <c r="Y37" s="33"/>
+      <c r="Z37" s="33"/>
+      <c r="AA37" s="33"/>
+      <c r="AB37" s="47"/>
+      <c r="AC37" s="47"/>
+      <c r="AD37" s="33"/>
+      <c r="AE37" s="33"/>
+      <c r="AF37" s="33"/>
+      <c r="AG37" s="62"/>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="31">
+      <c r="A38" s="30">
         <v>33</v>
       </c>
-      <c r="B38" s="60" t="s">
+      <c r="B38" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="F38" s="33"/>
-      <c r="G38" s="60" t="s">
+      <c r="D38" s="32"/>
+      <c r="E38" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" s="32"/>
+      <c r="G38" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="H38" s="31" t="s">
+      <c r="H38" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="30">
         <v>15</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="30">
         <v>15</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="30">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L38" s="61">
+      <c r="L38" s="54">
         <f t="shared" si="1"/>
         <v>46345</v>
       </c>
-      <c r="M38" s="61">
+      <c r="M38" s="54">
         <f t="shared" si="2"/>
         <v>46351</v>
       </c>
-      <c r="N38" s="31" t="s">
+      <c r="N38" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
-      <c r="S38" s="34"/>
-      <c r="T38" s="34"/>
-      <c r="U38" s="34"/>
-      <c r="V38" s="34"/>
-      <c r="W38" s="34"/>
-      <c r="X38" s="34"/>
-      <c r="Y38" s="34"/>
-      <c r="Z38" s="34"/>
-      <c r="AA38" s="34"/>
-      <c r="AB38" s="34"/>
-      <c r="AC38" s="51"/>
-      <c r="AD38" s="34"/>
-      <c r="AE38" s="34"/>
-      <c r="AF38" s="34"/>
-      <c r="AG38" s="81"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="33"/>
+      <c r="S38" s="33"/>
+      <c r="T38" s="33"/>
+      <c r="U38" s="33"/>
+      <c r="V38" s="33"/>
+      <c r="W38" s="33"/>
+      <c r="X38" s="33"/>
+      <c r="Y38" s="33"/>
+      <c r="Z38" s="33"/>
+      <c r="AA38" s="33"/>
+      <c r="AB38" s="33"/>
+      <c r="AC38" s="47"/>
+      <c r="AD38" s="33"/>
+      <c r="AE38" s="33"/>
+      <c r="AF38" s="33"/>
+      <c r="AG38" s="62"/>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="31">
+      <c r="A39" s="30">
         <v>34</v>
       </c>
-      <c r="B39" s="60" t="s">
+      <c r="B39" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="F39" s="33"/>
-      <c r="G39" s="60" t="s">
+      <c r="D39" s="32"/>
+      <c r="E39" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" s="32"/>
+      <c r="G39" s="53" t="s">
         <v>159</v>
       </c>
-      <c r="H39" s="31" t="s">
+      <c r="H39" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="30">
         <v>15</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="30">
         <v>16</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="30">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L39" s="61">
+      <c r="L39" s="54">
         <f t="shared" si="1"/>
         <v>46345</v>
       </c>
-      <c r="M39" s="61">
+      <c r="M39" s="54">
         <f t="shared" si="2"/>
         <v>46358</v>
       </c>
-      <c r="N39" s="31" t="s">
+      <c r="N39" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="34"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="34"/>
-      <c r="V39" s="34"/>
-      <c r="W39" s="34"/>
-      <c r="X39" s="34"/>
-      <c r="Y39" s="34"/>
-      <c r="Z39" s="34"/>
-      <c r="AA39" s="34"/>
-      <c r="AB39" s="34"/>
-      <c r="AC39" s="51"/>
-      <c r="AD39" s="51"/>
-      <c r="AE39" s="34"/>
-      <c r="AF39" s="34"/>
-      <c r="AG39" s="81"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="33"/>
+      <c r="S39" s="33"/>
+      <c r="T39" s="33"/>
+      <c r="U39" s="33"/>
+      <c r="V39" s="33"/>
+      <c r="W39" s="33"/>
+      <c r="X39" s="33"/>
+      <c r="Y39" s="33"/>
+      <c r="Z39" s="33"/>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="33"/>
+      <c r="AC39" s="47"/>
+      <c r="AD39" s="47"/>
+      <c r="AE39" s="33"/>
+      <c r="AF39" s="33"/>
+      <c r="AG39" s="62"/>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A40" s="31">
+      <c r="A40" s="30">
         <v>35</v>
       </c>
-      <c r="B40" s="60" t="s">
+      <c r="B40" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="32" t="s">
+      <c r="C40" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" s="33"/>
-      <c r="G40" s="60" t="s">
+      <c r="D40" s="32"/>
+      <c r="E40" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" s="32"/>
+      <c r="G40" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="H40" s="31" t="s">
+      <c r="H40" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="30">
         <v>16</v>
       </c>
-      <c r="J40" s="31">
+      <c r="J40" s="30">
         <v>16</v>
       </c>
-      <c r="K40" s="31">
+      <c r="K40" s="30">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L40" s="61">
+      <c r="L40" s="54">
         <f t="shared" si="1"/>
         <v>46352</v>
       </c>
-      <c r="M40" s="61">
+      <c r="M40" s="54">
         <f t="shared" si="2"/>
         <v>46358</v>
       </c>
-      <c r="N40" s="31" t="s">
+      <c r="N40" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="O40" s="34"/>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="34"/>
-      <c r="S40" s="34"/>
-      <c r="T40" s="34"/>
-      <c r="U40" s="34"/>
-      <c r="V40" s="34"/>
-      <c r="W40" s="34"/>
-      <c r="X40" s="34"/>
-      <c r="Y40" s="34"/>
-      <c r="Z40" s="34"/>
-      <c r="AA40" s="34"/>
-      <c r="AB40" s="34"/>
-      <c r="AC40" s="34"/>
-      <c r="AD40" s="51"/>
-      <c r="AE40" s="34"/>
-      <c r="AF40" s="34"/>
-      <c r="AG40" s="81"/>
+      <c r="O40" s="33"/>
+      <c r="P40" s="33"/>
+      <c r="Q40" s="33"/>
+      <c r="R40" s="33"/>
+      <c r="S40" s="33"/>
+      <c r="T40" s="33"/>
+      <c r="U40" s="33"/>
+      <c r="V40" s="33"/>
+      <c r="W40" s="33"/>
+      <c r="X40" s="33"/>
+      <c r="Y40" s="33"/>
+      <c r="Z40" s="33"/>
+      <c r="AA40" s="33"/>
+      <c r="AB40" s="33"/>
+      <c r="AC40" s="33"/>
+      <c r="AD40" s="47"/>
+      <c r="AE40" s="33"/>
+      <c r="AF40" s="33"/>
+      <c r="AG40" s="62"/>
     </row>
     <row r="41" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="42">
+      <c r="A41" s="40">
         <v>36</v>
       </c>
-      <c r="B41" s="44" t="s">
+      <c r="B41" s="42" t="s">
         <v>74</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" s="42"/>
-      <c r="G41" s="44" t="s">
+      <c r="D41" s="40"/>
+      <c r="E41" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" s="40"/>
+      <c r="G41" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="H41" s="42" t="s">
+      <c r="H41" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="I41" s="42">
+      <c r="I41" s="40">
         <v>16</v>
       </c>
-      <c r="J41" s="42">
+      <c r="J41" s="40">
         <v>16</v>
       </c>
-      <c r="K41" s="42">
+      <c r="K41" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L41" s="46">
+      <c r="L41" s="43">
         <f t="shared" si="1"/>
         <v>46352</v>
       </c>
-      <c r="M41" s="46">
+      <c r="M41" s="43">
         <f t="shared" si="2"/>
         <v>46358</v>
       </c>
-      <c r="N41" s="42" t="s">
+      <c r="N41" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="O41" s="34"/>
-      <c r="P41" s="34"/>
-      <c r="Q41" s="34"/>
-      <c r="R41" s="34"/>
-      <c r="S41" s="34"/>
-      <c r="T41" s="34"/>
-      <c r="U41" s="34"/>
-      <c r="V41" s="34"/>
-      <c r="W41" s="34"/>
-      <c r="X41" s="34"/>
-      <c r="Y41" s="34"/>
-      <c r="Z41" s="34"/>
-      <c r="AA41" s="34"/>
-      <c r="AB41" s="34"/>
-      <c r="AC41" s="34"/>
-      <c r="AD41" s="47" t="s">
+      <c r="O41" s="33"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="33"/>
+      <c r="R41" s="33"/>
+      <c r="S41" s="33"/>
+      <c r="T41" s="33"/>
+      <c r="U41" s="33"/>
+      <c r="V41" s="33"/>
+      <c r="W41" s="33"/>
+      <c r="X41" s="33"/>
+      <c r="Y41" s="33"/>
+      <c r="Z41" s="33"/>
+      <c r="AA41" s="33"/>
+      <c r="AB41" s="33"/>
+      <c r="AC41" s="33"/>
+      <c r="AD41" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="AE41" s="34"/>
-      <c r="AF41" s="34"/>
-      <c r="AG41" s="81"/>
+      <c r="AE41" s="33"/>
+      <c r="AF41" s="33"/>
+      <c r="AG41" s="62"/>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="37">
+      <c r="A42" s="35">
         <v>37</v>
       </c>
-      <c r="B42" s="62" t="s">
+      <c r="B42" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C42" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G42" s="62" t="s">
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="H42" s="37" t="s">
+      <c r="H42" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="I42" s="37">
+      <c r="I42" s="35">
         <v>17</v>
       </c>
-      <c r="J42" s="37">
+      <c r="J42" s="35">
         <v>17</v>
       </c>
-      <c r="K42" s="37">
+      <c r="K42" s="35">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L42" s="63">
+      <c r="L42" s="56">
         <f t="shared" si="1"/>
         <v>46359</v>
       </c>
-      <c r="M42" s="63">
+      <c r="M42" s="56">
         <f t="shared" si="2"/>
         <v>46365</v>
       </c>
-      <c r="N42" s="37" t="s">
+      <c r="N42" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="O42" s="34"/>
-      <c r="P42" s="34"/>
-      <c r="Q42" s="34"/>
-      <c r="R42" s="34"/>
-      <c r="S42" s="34"/>
-      <c r="T42" s="34"/>
-      <c r="U42" s="34"/>
-      <c r="V42" s="34"/>
-      <c r="W42" s="34"/>
-      <c r="X42" s="34"/>
-      <c r="Y42" s="34"/>
-      <c r="Z42" s="34"/>
-      <c r="AA42" s="34"/>
-      <c r="AB42" s="34"/>
-      <c r="AC42" s="34"/>
-      <c r="AD42" s="34"/>
-      <c r="AE42" s="51"/>
-      <c r="AF42" s="34"/>
-      <c r="AG42" s="81"/>
+      <c r="O42" s="33"/>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="33"/>
+      <c r="R42" s="33"/>
+      <c r="S42" s="33"/>
+      <c r="T42" s="33"/>
+      <c r="U42" s="33"/>
+      <c r="V42" s="33"/>
+      <c r="W42" s="33"/>
+      <c r="X42" s="33"/>
+      <c r="Y42" s="33"/>
+      <c r="Z42" s="33"/>
+      <c r="AA42" s="33"/>
+      <c r="AB42" s="33"/>
+      <c r="AC42" s="33"/>
+      <c r="AD42" s="33"/>
+      <c r="AE42" s="47"/>
+      <c r="AF42" s="33"/>
+      <c r="AG42" s="62"/>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" s="37">
+      <c r="A43" s="35">
         <v>38</v>
       </c>
-      <c r="B43" s="62" t="s">
+      <c r="B43" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="38" t="s">
+      <c r="C43" s="36" t="s">
         <v>209</v>
       </c>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G43" s="62" t="s">
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G43" s="55" t="s">
         <v>128</v>
       </c>
-      <c r="H43" s="37" t="s">
+      <c r="H43" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="I43" s="37">
+      <c r="I43" s="35">
         <v>17</v>
       </c>
-      <c r="J43" s="37">
+      <c r="J43" s="35">
         <v>17</v>
       </c>
-      <c r="K43" s="37">
+      <c r="K43" s="35">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L43" s="63">
+      <c r="L43" s="56">
         <f t="shared" si="1"/>
         <v>46359</v>
       </c>
-      <c r="M43" s="63">
+      <c r="M43" s="56">
         <f t="shared" si="2"/>
         <v>46365</v>
       </c>
-      <c r="N43" s="37" t="s">
+      <c r="N43" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="O43" s="34"/>
-      <c r="P43" s="34"/>
-      <c r="Q43" s="34"/>
-      <c r="R43" s="34"/>
-      <c r="S43" s="34"/>
-      <c r="T43" s="34"/>
-      <c r="U43" s="34"/>
-      <c r="V43" s="34"/>
-      <c r="W43" s="34"/>
-      <c r="X43" s="34"/>
-      <c r="Y43" s="34"/>
-      <c r="Z43" s="34"/>
-      <c r="AA43" s="34"/>
-      <c r="AB43" s="34"/>
-      <c r="AC43" s="34"/>
-      <c r="AD43" s="34"/>
-      <c r="AE43" s="51"/>
-      <c r="AF43" s="34"/>
-      <c r="AG43" s="81"/>
+      <c r="O43" s="33"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="33"/>
+      <c r="R43" s="33"/>
+      <c r="S43" s="33"/>
+      <c r="T43" s="33"/>
+      <c r="U43" s="33"/>
+      <c r="V43" s="33"/>
+      <c r="W43" s="33"/>
+      <c r="X43" s="33"/>
+      <c r="Y43" s="33"/>
+      <c r="Z43" s="33"/>
+      <c r="AA43" s="33"/>
+      <c r="AB43" s="33"/>
+      <c r="AC43" s="33"/>
+      <c r="AD43" s="33"/>
+      <c r="AE43" s="47"/>
+      <c r="AF43" s="33"/>
+      <c r="AG43" s="62"/>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="37">
+      <c r="A44" s="35">
         <v>39</v>
       </c>
-      <c r="B44" s="62" t="s">
+      <c r="B44" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="C44" s="38" t="s">
+      <c r="C44" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G44" s="62" t="s">
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" s="55" t="s">
         <v>128</v>
       </c>
-      <c r="H44" s="37" t="s">
+      <c r="H44" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="I44" s="37">
+      <c r="I44" s="35">
         <v>17</v>
       </c>
-      <c r="J44" s="37">
+      <c r="J44" s="35">
         <v>18</v>
       </c>
-      <c r="K44" s="37">
+      <c r="K44" s="35">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L44" s="63">
+      <c r="L44" s="56">
         <f t="shared" si="1"/>
         <v>46359</v>
       </c>
-      <c r="M44" s="63">
+      <c r="M44" s="56">
         <f t="shared" si="2"/>
         <v>46372</v>
       </c>
-      <c r="N44" s="37" t="s">
+      <c r="N44" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="O44" s="34"/>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="34"/>
-      <c r="R44" s="34"/>
-      <c r="S44" s="34"/>
-      <c r="T44" s="34"/>
-      <c r="U44" s="34"/>
-      <c r="V44" s="34"/>
-      <c r="W44" s="34"/>
-      <c r="X44" s="34"/>
-      <c r="Y44" s="34"/>
-      <c r="Z44" s="34"/>
-      <c r="AA44" s="34"/>
-      <c r="AB44" s="34"/>
-      <c r="AC44" s="34"/>
-      <c r="AD44" s="34"/>
-      <c r="AE44" s="51"/>
-      <c r="AF44" s="51"/>
-      <c r="AG44" s="81"/>
+      <c r="O44" s="33"/>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="33"/>
+      <c r="S44" s="33"/>
+      <c r="T44" s="33"/>
+      <c r="U44" s="33"/>
+      <c r="V44" s="33"/>
+      <c r="W44" s="33"/>
+      <c r="X44" s="33"/>
+      <c r="Y44" s="33"/>
+      <c r="Z44" s="33"/>
+      <c r="AA44" s="33"/>
+      <c r="AB44" s="33"/>
+      <c r="AC44" s="33"/>
+      <c r="AD44" s="33"/>
+      <c r="AE44" s="47"/>
+      <c r="AF44" s="47"/>
+      <c r="AG44" s="62"/>
     </row>
     <row r="45" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="42">
+      <c r="A45" s="40">
         <v>40</v>
       </c>
-      <c r="B45" s="44" t="s">
+      <c r="B45" s="42" t="s">
         <v>79</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="G45" s="44" t="s">
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G45" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="H45" s="42" t="s">
+      <c r="H45" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="I45" s="42">
+      <c r="I45" s="40">
         <v>18</v>
       </c>
-      <c r="J45" s="42">
+      <c r="J45" s="40">
         <v>18</v>
       </c>
-      <c r="K45" s="42">
+      <c r="K45" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L45" s="46">
+      <c r="L45" s="43">
         <f t="shared" si="1"/>
         <v>46366</v>
       </c>
-      <c r="M45" s="46">
+      <c r="M45" s="43">
         <f t="shared" si="2"/>
         <v>46372</v>
       </c>
-      <c r="N45" s="42" t="s">
+      <c r="N45" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="O45" s="34"/>
-      <c r="P45" s="34"/>
-      <c r="Q45" s="34"/>
-      <c r="R45" s="34"/>
-      <c r="S45" s="34"/>
-      <c r="T45" s="34"/>
-      <c r="U45" s="34"/>
-      <c r="V45" s="34"/>
-      <c r="W45" s="34"/>
-      <c r="X45" s="34"/>
-      <c r="Y45" s="34"/>
-      <c r="Z45" s="34"/>
-      <c r="AA45" s="34"/>
-      <c r="AB45" s="34"/>
-      <c r="AC45" s="34"/>
-      <c r="AD45" s="34"/>
-      <c r="AE45" s="34"/>
-      <c r="AF45" s="47" t="s">
+      <c r="O45" s="33"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="33"/>
+      <c r="R45" s="33"/>
+      <c r="S45" s="33"/>
+      <c r="T45" s="33"/>
+      <c r="U45" s="33"/>
+      <c r="V45" s="33"/>
+      <c r="W45" s="33"/>
+      <c r="X45" s="33"/>
+      <c r="Y45" s="33"/>
+      <c r="Z45" s="33"/>
+      <c r="AA45" s="33"/>
+      <c r="AB45" s="33"/>
+      <c r="AC45" s="33"/>
+      <c r="AD45" s="33"/>
+      <c r="AE45" s="33"/>
+      <c r="AF45" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="AG45" s="81"/>
+      <c r="AG45" s="62"/>
     </row>
     <row r="46" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="42">
+      <c r="A46" s="40">
         <v>41</v>
       </c>
-      <c r="B46" s="44" t="s">
+      <c r="B46" s="42" t="s">
         <v>79</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="G46" s="44" t="s">
+      <c r="D46" s="40"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G46" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="H46" s="42" t="s">
+      <c r="H46" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="I46" s="42">
+      <c r="I46" s="40">
         <v>18</v>
       </c>
-      <c r="J46" s="42">
+      <c r="J46" s="40">
         <v>18</v>
       </c>
-      <c r="K46" s="42">
+      <c r="K46" s="40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L46" s="46">
+      <c r="L46" s="43">
         <f t="shared" si="1"/>
         <v>46366</v>
       </c>
-      <c r="M46" s="46">
+      <c r="M46" s="43">
         <f t="shared" si="2"/>
         <v>46372</v>
       </c>
-      <c r="N46" s="42" t="s">
+      <c r="N46" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="O46" s="34"/>
-      <c r="P46" s="34"/>
-      <c r="Q46" s="34"/>
-      <c r="R46" s="34"/>
-      <c r="S46" s="34"/>
-      <c r="T46" s="34"/>
-      <c r="U46" s="34"/>
-      <c r="V46" s="34"/>
-      <c r="W46" s="34"/>
-      <c r="X46" s="34"/>
-      <c r="Y46" s="34"/>
-      <c r="Z46" s="34"/>
-      <c r="AA46" s="34"/>
-      <c r="AB46" s="34"/>
-      <c r="AC46" s="34"/>
-      <c r="AD46" s="34"/>
-      <c r="AE46" s="34"/>
-      <c r="AF46" s="47" t="s">
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="33"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="33"/>
+      <c r="X46" s="33"/>
+      <c r="Y46" s="33"/>
+      <c r="Z46" s="33"/>
+      <c r="AA46" s="33"/>
+      <c r="AB46" s="33"/>
+      <c r="AC46" s="33"/>
+      <c r="AD46" s="33"/>
+      <c r="AE46" s="33"/>
+      <c r="AF46" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="AG46" s="81"/>
+      <c r="AG46" s="62"/>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A47" s="40">
+      <c r="A47" s="38">
         <v>42</v>
       </c>
-      <c r="B47" s="64" t="s">
+      <c r="B47" s="57" t="s">
         <v>190</v>
       </c>
-      <c r="C47" s="41" t="s">
+      <c r="C47" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="D47" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E47" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="F47" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="G47" s="64" t="s">
+      <c r="D47" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="H47" s="40" t="s">
+      <c r="H47" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="I47" s="40">
+      <c r="I47" s="38">
         <v>1</v>
       </c>
-      <c r="J47" s="40">
+      <c r="J47" s="38">
         <v>18</v>
       </c>
-      <c r="K47" s="40">
+      <c r="K47" s="38">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="L47" s="65">
+      <c r="L47" s="58">
         <f t="shared" si="1"/>
         <v>46247</v>
       </c>
-      <c r="M47" s="65">
+      <c r="M47" s="58">
         <f t="shared" si="2"/>
         <v>46372</v>
       </c>
-      <c r="N47" s="40" t="s">
+      <c r="N47" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="O47" s="56"/>
-      <c r="P47" s="56"/>
-      <c r="Q47" s="56"/>
-      <c r="R47" s="56"/>
-      <c r="S47" s="56"/>
-      <c r="T47" s="56"/>
-      <c r="U47" s="56"/>
-      <c r="V47" s="56"/>
-      <c r="W47" s="56"/>
-      <c r="X47" s="56"/>
-      <c r="Y47" s="56"/>
-      <c r="Z47" s="56"/>
-      <c r="AA47" s="56"/>
-      <c r="AB47" s="56"/>
-      <c r="AC47" s="56"/>
-      <c r="AD47" s="56"/>
-      <c r="AE47" s="56"/>
-      <c r="AF47" s="56"/>
-      <c r="AG47" s="81"/>
+      <c r="O47" s="50"/>
+      <c r="P47" s="50"/>
+      <c r="Q47" s="50"/>
+      <c r="R47" s="50"/>
+      <c r="S47" s="50"/>
+      <c r="T47" s="50"/>
+      <c r="U47" s="50"/>
+      <c r="V47" s="50"/>
+      <c r="W47" s="50"/>
+      <c r="X47" s="50"/>
+      <c r="Y47" s="50"/>
+      <c r="Z47" s="50"/>
+      <c r="AA47" s="50"/>
+      <c r="AB47" s="50"/>
+      <c r="AC47" s="50"/>
+      <c r="AD47" s="50"/>
+      <c r="AE47" s="50"/>
+      <c r="AF47" s="50"/>
+      <c r="AG47" s="62"/>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="40">
+      <c r="A48" s="38">
         <v>43</v>
       </c>
-      <c r="B48" s="64" t="s">
+      <c r="B48" s="57" t="s">
         <v>190</v>
       </c>
-      <c r="C48" s="41" t="s">
+      <c r="C48" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="D48" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E48" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="F48" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="G48" s="64" t="s">
+      <c r="D48" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="H48" s="40" t="s">
+      <c r="H48" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="I48" s="40">
+      <c r="I48" s="38">
         <v>1</v>
       </c>
-      <c r="J48" s="40">
+      <c r="J48" s="38">
         <v>18</v>
       </c>
-      <c r="K48" s="40">
+      <c r="K48" s="38">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="L48" s="65">
+      <c r="L48" s="58">
         <f t="shared" si="1"/>
         <v>46247</v>
       </c>
-      <c r="M48" s="65">
+      <c r="M48" s="58">
         <f t="shared" si="2"/>
         <v>46372</v>
       </c>
-      <c r="N48" s="40" t="s">
+      <c r="N48" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="O48" s="56"/>
-      <c r="P48" s="56"/>
-      <c r="Q48" s="56"/>
-      <c r="R48" s="56"/>
-      <c r="S48" s="56"/>
-      <c r="T48" s="56"/>
-      <c r="U48" s="56"/>
-      <c r="V48" s="56"/>
-      <c r="W48" s="56"/>
-      <c r="X48" s="56"/>
-      <c r="Y48" s="56"/>
-      <c r="Z48" s="56"/>
-      <c r="AA48" s="56"/>
-      <c r="AB48" s="56"/>
-      <c r="AC48" s="56"/>
-      <c r="AD48" s="56"/>
-      <c r="AE48" s="56"/>
-      <c r="AF48" s="56"/>
-      <c r="AG48" s="81"/>
+      <c r="O48" s="50"/>
+      <c r="P48" s="50"/>
+      <c r="Q48" s="50"/>
+      <c r="R48" s="50"/>
+      <c r="S48" s="50"/>
+      <c r="T48" s="50"/>
+      <c r="U48" s="50"/>
+      <c r="V48" s="50"/>
+      <c r="W48" s="50"/>
+      <c r="X48" s="50"/>
+      <c r="Y48" s="50"/>
+      <c r="Z48" s="50"/>
+      <c r="AA48" s="50"/>
+      <c r="AB48" s="50"/>
+      <c r="AC48" s="50"/>
+      <c r="AD48" s="50"/>
+      <c r="AE48" s="50"/>
+      <c r="AF48" s="50"/>
+      <c r="AG48" s="62"/>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" s="40">
+      <c r="A49" s="38">
         <v>44</v>
       </c>
-      <c r="B49" s="64" t="s">
+      <c r="B49" s="57" t="s">
         <v>190</v>
       </c>
-      <c r="C49" s="41" t="s">
+      <c r="C49" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="D49" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E49" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="F49" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="G49" s="64" t="s">
+      <c r="D49" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="H49" s="40" t="s">
+      <c r="H49" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="I49" s="40">
+      <c r="I49" s="38">
         <v>1</v>
       </c>
-      <c r="J49" s="40">
+      <c r="J49" s="38">
         <v>18</v>
       </c>
-      <c r="K49" s="40">
+      <c r="K49" s="38">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="L49" s="65">
+      <c r="L49" s="58">
         <f t="shared" si="1"/>
         <v>46247</v>
       </c>
-      <c r="M49" s="65">
+      <c r="M49" s="58">
         <f t="shared" si="2"/>
         <v>46372</v>
       </c>
-      <c r="N49" s="40" t="s">
+      <c r="N49" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="O49" s="56"/>
-      <c r="P49" s="56"/>
-      <c r="Q49" s="56"/>
-      <c r="R49" s="56"/>
-      <c r="S49" s="56"/>
-      <c r="T49" s="56"/>
-      <c r="U49" s="56"/>
-      <c r="V49" s="56"/>
-      <c r="W49" s="56"/>
-      <c r="X49" s="56"/>
-      <c r="Y49" s="56"/>
-      <c r="Z49" s="56"/>
-      <c r="AA49" s="56"/>
-      <c r="AB49" s="56"/>
-      <c r="AC49" s="56"/>
-      <c r="AD49" s="56"/>
-      <c r="AE49" s="56"/>
-      <c r="AF49" s="56"/>
-      <c r="AG49" s="81"/>
+      <c r="O49" s="50"/>
+      <c r="P49" s="50"/>
+      <c r="Q49" s="50"/>
+      <c r="R49" s="50"/>
+      <c r="S49" s="50"/>
+      <c r="T49" s="50"/>
+      <c r="U49" s="50"/>
+      <c r="V49" s="50"/>
+      <c r="W49" s="50"/>
+      <c r="X49" s="50"/>
+      <c r="Y49" s="50"/>
+      <c r="Z49" s="50"/>
+      <c r="AA49" s="50"/>
+      <c r="AB49" s="50"/>
+      <c r="AC49" s="50"/>
+      <c r="AD49" s="50"/>
+      <c r="AE49" s="50"/>
+      <c r="AF49" s="50"/>
+      <c r="AG49" s="62"/>
     </row>
     <row r="50" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="66" t="s">
+      <c r="A51" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="B51" s="35" t="s">
+      <c r="B51" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="C51" s="67" t="s">
+      <c r="C51" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="E51" s="56" t="s">
+      <c r="E51" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="F51" s="67" t="s">
+      <c r="F51" s="60" t="s">
         <v>180</v>
       </c>
-      <c r="H51" s="51" t="s">
+      <c r="H51" s="47" t="s">
         <v>215</v>
       </c>
-      <c r="I51" s="67" t="s">
+      <c r="I51" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="K51" s="68" t="s">
+      <c r="K51" s="61" t="s">
         <v>215</v>
       </c>
-      <c r="L51" s="67" t="s">
+      <c r="L51" s="60" t="s">
         <v>216</v>
       </c>
     </row>
@@ -5507,67 +5486,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
     </row>
     <row r="4" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="79" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="73"/>
-      <c r="E4" s="79" t="s">
+      <c r="D4" s="67"/>
+      <c r="E4" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="73"/>
-      <c r="G4" s="79" t="s">
+      <c r="F4" s="67"/>
+      <c r="G4" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="73"/>
+      <c r="H4" s="67"/>
     </row>
     <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="77">
+      <c r="A5" s="71">
         <f>'Carta Gantt'!F3</f>
         <v>12</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="77">
+      <c r="B5" s="67"/>
+      <c r="C5" s="71">
         <v>18</v>
       </c>
-      <c r="D5" s="73"/>
-      <c r="E5" s="77">
+      <c r="D5" s="67"/>
+      <c r="E5" s="71">
         <f>COUNTIF('Carta Gantt'!$H$6:$H$49,"Hito")</f>
         <v>8</v>
       </c>
-      <c r="F5" s="73"/>
-      <c r="G5" s="80">
+      <c r="F5" s="67"/>
+      <c r="G5" s="74">
         <f>COUNTIFS('Carta Gantt'!$H$6:$H$49,"Tarea",'Carta Gantt'!$N$6:$N$49,"Completado")/COUNTIF('Carta Gantt'!$H$6:$H$49,"Tarea")</f>
         <v>0.3611111111111111</v>
       </c>
-      <c r="H5" s="73"/>
+      <c r="H5" s="67"/>
     </row>
     <row r="8" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -5596,28 +5575,28 @@
       <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="8" t="e">
-        <f ca="1">_xludf.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A9)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C9" s="8" t="e">
-        <f ca="1">_xludf.MAXIFS('Carta Gantt'!$J$6:$J$49,'Carta Gantt'!$B$6:$B$49,$A9)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D9" s="8" t="e">
-        <f t="shared" ref="D9:D15" ca="1" si="0">C9-B9+1</f>
-        <v>#NAME?</v>
+      <c r="B9" s="8">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A9)</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="8">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A9)</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A9)</f>
+        <v>1</v>
       </c>
       <c r="E9" s="8">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A9,'Carta Gantt'!$H$6:$H$49,"Tarea")</f>
-        <v>8</v>
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A9)</f>
+        <v>1</v>
       </c>
       <c r="F9" s="8">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A9,'Carta Gantt'!$H$6:$H$49,"Hito")</f>
-        <v>2</v>
-      </c>
-      <c r="G9" s="25">
-        <f>IF(COUNTIFS('Carta Gantt'!$B$6:$B$49,$A9,'Carta Gantt'!$H$6:$H$49,"Tarea")=0,0,COUNTIFS('Carta Gantt'!$B$6:$B$49,$A9,'Carta Gantt'!$H$6:$H$49,"Tarea",'Carta Gantt'!$N$6:$N$49,"Completado")/COUNTIFS('Carta Gantt'!$B$6:$B$49,$A9,'Carta Gantt'!$H$6:$H$49,"Tarea"))</f>
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A9)</f>
+        <v>1</v>
+      </c>
+      <c r="G9" s="8">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A9)</f>
         <v>1</v>
       </c>
     </row>
@@ -5625,174 +5604,174 @@
       <c r="A10" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="19" t="e">
-        <f ca="1">_xludf.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C10" s="19" t="e">
-        <f ca="1">_xludf.MAXIFS('Carta Gantt'!$J$6:$J$49,'Carta Gantt'!$B$6:$B$49,$A10)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D10" s="19" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+      <c r="B10" s="19">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A10)</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="19">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A10)</f>
+        <v>4</v>
+      </c>
+      <c r="D10" s="19">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A10)</f>
+        <v>4</v>
       </c>
       <c r="E10" s="19">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A10,'Carta Gantt'!$H$6:$H$49,"Tarea")</f>
-        <v>5</v>
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A10)</f>
+        <v>4</v>
       </c>
       <c r="F10" s="19">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A10,'Carta Gantt'!$H$6:$H$49,"Hito")</f>
-        <v>1</v>
-      </c>
-      <c r="G10" s="36">
-        <f>IF(COUNTIFS('Carta Gantt'!$B$6:$B$49,$A10,'Carta Gantt'!$H$6:$H$49,"Tarea")=0,0,COUNTIFS('Carta Gantt'!$B$6:$B$49,$A10,'Carta Gantt'!$H$6:$H$49,"Tarea",'Carta Gantt'!$N$6:$N$49,"Completado")/COUNTIFS('Carta Gantt'!$B$6:$B$49,$A10,'Carta Gantt'!$H$6:$H$49,"Tarea"))</f>
-        <v>0</v>
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A10)</f>
+        <v>4</v>
+      </c>
+      <c r="G10" s="19">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A10)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="2" t="e">
-        <f ca="1">_xludf.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A11)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C11" s="2" t="e">
-        <f ca="1">_xludf.MAXIFS('Carta Gantt'!$J$6:$J$49,'Carta Gantt'!$B$6:$B$49,$A11)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D11" s="2" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
+      <c r="B11" s="2">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A11)</f>
+        <v>7</v>
+      </c>
+      <c r="C11" s="2">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A11)</f>
+        <v>7</v>
+      </c>
+      <c r="D11" s="2">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A11)</f>
+        <v>7</v>
       </c>
       <c r="E11" s="2">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A11,'Carta Gantt'!$H$6:$H$49,"Tarea")</f>
-        <v>6</v>
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A11)</f>
+        <v>7</v>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A11,'Carta Gantt'!$H$6:$H$49,"Hito")</f>
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A11)</f>
+        <v>7</v>
+      </c>
+      <c r="G11" s="2">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A11)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="26">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A12)</f>
+        <v>10</v>
+      </c>
+      <c r="C12" s="26">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A12)</f>
+        <v>10</v>
+      </c>
+      <c r="D12" s="26">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A12)</f>
+        <v>10</v>
+      </c>
+      <c r="E12" s="26">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A12)</f>
+        <v>10</v>
+      </c>
+      <c r="F12" s="26">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A12)</f>
+        <v>10</v>
+      </c>
+      <c r="G12" s="26">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A12)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="30">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A13)</f>
+        <v>14</v>
+      </c>
+      <c r="C13" s="30">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A13)</f>
+        <v>14</v>
+      </c>
+      <c r="D13" s="30">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A13)</f>
+        <v>14</v>
+      </c>
+      <c r="E13" s="30">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A13)</f>
+        <v>14</v>
+      </c>
+      <c r="F13" s="30">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A13)</f>
+        <v>14</v>
+      </c>
+      <c r="G13" s="30">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A13)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="35">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A14)</f>
+        <v>17</v>
+      </c>
+      <c r="C14" s="35">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A14)</f>
+        <v>17</v>
+      </c>
+      <c r="D14" s="35">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A14)</f>
+        <v>17</v>
+      </c>
+      <c r="E14" s="35">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A14)</f>
+        <v>17</v>
+      </c>
+      <c r="F14" s="35">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A14)</f>
+        <v>17</v>
+      </c>
+      <c r="G14" s="35">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A14)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="B15" s="38">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A15)</f>
         <v>1</v>
       </c>
-      <c r="G11" s="45">
-        <f>IF(COUNTIFS('Carta Gantt'!$B$6:$B$49,$A11,'Carta Gantt'!$H$6:$H$49,"Tarea")=0,0,COUNTIFS('Carta Gantt'!$B$6:$B$49,$A11,'Carta Gantt'!$H$6:$H$49,"Tarea",'Carta Gantt'!$N$6:$N$49,"Completado")/COUNTIFS('Carta Gantt'!$B$6:$B$49,$A11,'Carta Gantt'!$H$6:$H$49,"Tarea"))</f>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="27" t="e">
-        <f ca="1">_xludf.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A12)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C12" s="27" t="e">
-        <f ca="1">_xludf.MAXIFS('Carta Gantt'!$J$6:$J$49,'Carta Gantt'!$B$6:$B$49,$A12)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D12" s="27" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="E12" s="27">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A12,'Carta Gantt'!$H$6:$H$49,"Tarea")</f>
-        <v>6</v>
-      </c>
-      <c r="F12" s="27">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A12,'Carta Gantt'!$H$6:$H$49,"Hito")</f>
+      <c r="C15" s="38">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A15)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="49">
-        <f>IF(COUNTIFS('Carta Gantt'!$B$6:$B$49,$A12,'Carta Gantt'!$H$6:$H$49,"Tarea")=0,0,COUNTIFS('Carta Gantt'!$B$6:$B$49,$A12,'Carta Gantt'!$H$6:$H$49,"Tarea",'Carta Gantt'!$N$6:$N$49,"Completado")/COUNTIFS('Carta Gantt'!$B$6:$B$49,$A12,'Carta Gantt'!$H$6:$H$49,"Tarea"))</f>
-        <v>0.16666666666666666</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="31" t="e">
-        <f ca="1">_xludf.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A13)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C13" s="31" t="e">
-        <f ca="1">_xludf.MAXIFS('Carta Gantt'!$J$6:$J$49,'Carta Gantt'!$B$6:$B$49,$A13)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D13" s="31" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="E13" s="31">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A13,'Carta Gantt'!$H$6:$H$49,"Tarea")</f>
-        <v>5</v>
-      </c>
-      <c r="F13" s="31">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A13,'Carta Gantt'!$H$6:$H$49,"Hito")</f>
+      <c r="D15" s="38">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A15)</f>
         <v>1</v>
       </c>
-      <c r="G13" s="53">
-        <f>IF(COUNTIFS('Carta Gantt'!$B$6:$B$49,$A13,'Carta Gantt'!$H$6:$H$49,"Tarea")=0,0,COUNTIFS('Carta Gantt'!$B$6:$B$49,$A13,'Carta Gantt'!$H$6:$H$49,"Tarea",'Carta Gantt'!$N$6:$N$49,"Completado")/COUNTIFS('Carta Gantt'!$B$6:$B$49,$A13,'Carta Gantt'!$H$6:$H$49,"Tarea"))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="37" t="e">
-        <f ca="1">_xludf.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C14" s="37" t="e">
-        <f ca="1">_xludf.MAXIFS('Carta Gantt'!$J$6:$J$49,'Carta Gantt'!$B$6:$B$49,$A14)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D14" s="37" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="E14" s="37">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A14,'Carta Gantt'!$H$6:$H$49,"Tarea")</f>
-        <v>3</v>
-      </c>
-      <c r="F14" s="37">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A14,'Carta Gantt'!$H$6:$H$49,"Hito")</f>
-        <v>2</v>
-      </c>
-      <c r="G14" s="55">
-        <f>IF(COUNTIFS('Carta Gantt'!$B$6:$B$49,$A14,'Carta Gantt'!$H$6:$H$49,"Tarea")=0,0,COUNTIFS('Carta Gantt'!$B$6:$B$49,$A14,'Carta Gantt'!$H$6:$H$49,"Tarea",'Carta Gantt'!$N$6:$N$49,"Completado")/COUNTIFS('Carta Gantt'!$B$6:$B$49,$A14,'Carta Gantt'!$H$6:$H$49,"Tarea"))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="B15" s="40" t="e">
-        <f ca="1">_xludf.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C15" s="40" t="e">
-        <f ca="1">_xludf.MAXIFS('Carta Gantt'!$J$6:$J$49,'Carta Gantt'!$B$6:$B$49,$A15)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D15" s="40" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="E15" s="40">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A15,'Carta Gantt'!$H$6:$H$49,"Tarea")</f>
-        <v>3</v>
-      </c>
-      <c r="F15" s="40">
-        <f>COUNTIFS('Carta Gantt'!$B$6:$B$49,$A15,'Carta Gantt'!$H$6:$H$49,"Hito")</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="57">
-        <f>IF(COUNTIFS('Carta Gantt'!$B$6:$B$49,$A15,'Carta Gantt'!$H$6:$H$49,"Tarea")=0,0,COUNTIFS('Carta Gantt'!$B$6:$B$49,$A15,'Carta Gantt'!$H$6:$H$49,"Tarea",'Carta Gantt'!$N$6:$N$49,"Completado")/COUNTIFS('Carta Gantt'!$B$6:$B$49,$A15,'Carta Gantt'!$H$6:$H$49,"Tarea"))</f>
-        <v>0</v>
+      <c r="E15" s="38">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A15)</f>
+        <v>1</v>
+      </c>
+      <c r="F15" s="38">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A15)</f>
+        <v>1</v>
+      </c>
+      <c r="G15" s="38">
+        <f>_xlfn.MINIFS('Carta Gantt'!$I$6:$I$49,'Carta Gantt'!$B$6:$B$49,$A15)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -6815,13 +6794,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -8034,24 +8013,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -8442,98 +8421,98 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27">
+      <c r="A28" s="26">
         <v>24</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="29"/>
-      <c r="F28" s="28" t="s">
+      <c r="C28" s="28"/>
+      <c r="D28" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="28"/>
+      <c r="F28" s="27" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="27">
+      <c r="A29" s="26">
         <v>25</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="28" t="s">
+      <c r="C29" s="28"/>
+      <c r="D29" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="28"/>
+      <c r="F29" s="27" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27">
+      <c r="A30" s="26">
         <v>26</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="28" t="s">
+      <c r="C30" s="28"/>
+      <c r="D30" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="28"/>
+      <c r="F30" s="27" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="27">
+      <c r="A31" s="26">
         <v>27</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="29"/>
-      <c r="F31" s="28" t="s">
+      <c r="C31" s="28"/>
+      <c r="D31" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="28"/>
+      <c r="F31" s="27" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="27">
+      <c r="A32" s="26">
         <v>28</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" s="29"/>
-      <c r="F32" s="28" t="s">
+      <c r="C32" s="28"/>
+      <c r="D32" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="28"/>
+      <c r="F32" s="27" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="27">
+      <c r="A33" s="26">
         <v>29</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="28" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" s="28"/>
+      <c r="F33" s="27" t="s">
         <v>141</v>
       </c>
     </row>
@@ -8554,82 +8533,82 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="31">
+      <c r="A35" s="30">
         <v>31</v>
       </c>
-      <c r="B35" s="32" t="s">
+      <c r="B35" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="33"/>
-      <c r="F35" s="32" t="s">
+      <c r="C35" s="32"/>
+      <c r="D35" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="32"/>
+      <c r="F35" s="31" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="31">
-        <v>32</v>
-      </c>
-      <c r="B36" s="32" t="s">
+      <c r="A36" s="30">
+        <v>32</v>
+      </c>
+      <c r="B36" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" s="33"/>
-      <c r="F36" s="32" t="s">
+      <c r="C36" s="32"/>
+      <c r="D36" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" s="32"/>
+      <c r="F36" s="31" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="31">
+      <c r="A37" s="30">
         <v>33</v>
       </c>
-      <c r="B37" s="32" t="s">
+      <c r="B37" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="E37" s="33"/>
-      <c r="F37" s="32" t="s">
+      <c r="C37" s="32"/>
+      <c r="D37" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="32"/>
+      <c r="F37" s="31" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="31">
+      <c r="A38" s="30">
         <v>34</v>
       </c>
-      <c r="B38" s="32" t="s">
+      <c r="B38" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="E38" s="33"/>
-      <c r="F38" s="32" t="s">
+      <c r="C38" s="32"/>
+      <c r="D38" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="32"/>
+      <c r="F38" s="31" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="31">
+      <c r="A39" s="30">
         <v>35</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" s="33"/>
-      <c r="F39" s="32" t="s">
+      <c r="C39" s="32"/>
+      <c r="D39" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="32"/>
+      <c r="F39" s="31" t="s">
         <v>154</v>
       </c>
     </row>
@@ -8650,50 +8629,50 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="37">
+      <c r="A41" s="35">
         <v>37</v>
       </c>
-      <c r="B41" s="38" t="s">
+      <c r="B41" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" s="38" t="s">
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" s="36" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="37">
+      <c r="A42" s="35">
         <v>38</v>
       </c>
-      <c r="B42" s="38" t="s">
+      <c r="B42" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="F42" s="38" t="s">
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" s="36" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="37">
+      <c r="A43" s="35">
         <v>39</v>
       </c>
-      <c r="B43" s="38" t="s">
+      <c r="B43" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="F43" s="38" t="s">
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" s="36" t="s">
         <v>164</v>
       </c>
     </row>
@@ -8730,62 +8709,62 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="40">
+      <c r="A46" s="38">
         <v>42</v>
       </c>
-      <c r="B46" s="41" t="s">
+      <c r="B46" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="C46" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E46" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" s="41" t="s">
+      <c r="C46" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E46" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" s="39" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="40">
+      <c r="A47" s="38">
         <v>43</v>
       </c>
-      <c r="B47" s="41" t="s">
+      <c r="B47" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="C47" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="D47" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E47" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="F47" s="41" t="s">
+      <c r="C47" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" s="39" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="40">
+      <c r="A48" s="38">
         <v>44</v>
       </c>
-      <c r="B48" s="41" t="s">
+      <c r="B48" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="C48" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="D48" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E48" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="F48" s="41" t="s">
+      <c r="C48" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" s="39" t="s">
         <v>175</v>
       </c>
     </row>
